--- a/output/laminas_comunales/comunal_i_ingr_a_2022_los_lagos.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_a_2022_los_lagos.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -396,9 +391,6 @@
       <c r="B2">
         <v>1257646.88</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -409,9 +401,6 @@
       <c r="B3">
         <v>984058.4399999999</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -422,9 +411,6 @@
       <c r="B4">
         <v>977059.62</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -435,9 +421,6 @@
       <c r="B5">
         <v>975423.9399999999</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -448,9 +431,6 @@
       <c r="B6">
         <v>948858.9399999999</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -461,9 +441,6 @@
       <c r="B7">
         <v>947986.62</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -474,9 +451,6 @@
       <c r="B8">
         <v>941105.75</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -487,9 +461,6 @@
       <c r="B9">
         <v>935867.9399999999</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -500,9 +471,6 @@
       <c r="B10">
         <v>930150</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -513,9 +481,6 @@
       <c r="B11">
         <v>909668.0600000001</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -526,9 +491,6 @@
       <c r="B12">
         <v>893820.5</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -539,9 +501,6 @@
       <c r="B13">
         <v>892700.62</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -552,9 +511,6 @@
       <c r="B14">
         <v>888627.5</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -565,9 +521,6 @@
       <c r="B15">
         <v>886353.9399999999</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -578,9 +531,6 @@
       <c r="B16">
         <v>879155.88</v>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -591,9 +541,6 @@
       <c r="B17">
         <v>866403.25</v>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -604,9 +551,6 @@
       <c r="B18">
         <v>862841.0600000001</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -617,9 +561,6 @@
       <c r="B19">
         <v>858706.1899999999</v>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -630,9 +571,6 @@
       <c r="B20">
         <v>856643.38</v>
       </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -643,9 +581,6 @@
       <c r="B21">
         <v>843365.1899999999</v>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -656,9 +591,6 @@
       <c r="B22">
         <v>835448.8100000001</v>
       </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -669,9 +601,6 @@
       <c r="B23">
         <v>797679.0600000001</v>
       </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -682,9 +611,6 @@
       <c r="B24">
         <v>778819.4399999999</v>
       </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -695,9 +621,6 @@
       <c r="B25">
         <v>773275.4399999999</v>
       </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -708,9 +631,6 @@
       <c r="B26">
         <v>767498.38</v>
       </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -721,9 +641,6 @@
       <c r="B27">
         <v>763313.9399999999</v>
       </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -734,9 +651,6 @@
       <c r="B28">
         <v>763173.9399999999</v>
       </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -747,9 +661,6 @@
       <c r="B29">
         <v>759157.12</v>
       </c>
-      <c r="F29" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -760,9 +671,6 @@
       <c r="B30">
         <v>743177.5600000001</v>
       </c>
-      <c r="F30" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -772,9 +680,6 @@
       </c>
       <c r="B31">
         <v>687087.88</v>
-      </c>
-      <c r="F31" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_a_2022_los_lagos.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_a_2022_los_lagos.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -391,6 +391,15 @@
       <c r="B2">
         <v>1257646.88</v>
       </c>
+      <c r="C2">
+        <v>1122541</v>
+      </c>
+      <c r="D2">
+        <v>135105.8799999999</v>
+      </c>
+      <c r="E2">
+        <v>12.03571896260358</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -401,6 +410,15 @@
       <c r="B3">
         <v>984058.4399999999</v>
       </c>
+      <c r="C3">
+        <v>888085.0600000001</v>
+      </c>
+      <c r="D3">
+        <v>95973.37999999989</v>
+      </c>
+      <c r="E3">
+        <v>10.80677790030606</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -411,6 +429,15 @@
       <c r="B4">
         <v>977059.62</v>
       </c>
+      <c r="C4">
+        <v>809486.4399999999</v>
+      </c>
+      <c r="D4">
+        <v>167573.1800000001</v>
+      </c>
+      <c r="E4">
+        <v>20.70117196774785</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -421,6 +448,15 @@
       <c r="B5">
         <v>975423.9399999999</v>
       </c>
+      <c r="C5">
+        <v>874962.75</v>
+      </c>
+      <c r="D5">
+        <v>100461.1899999999</v>
+      </c>
+      <c r="E5">
+        <v>11.48176765239435</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -431,6 +467,15 @@
       <c r="B6">
         <v>948858.9399999999</v>
       </c>
+      <c r="C6">
+        <v>789140.1899999999</v>
+      </c>
+      <c r="D6">
+        <v>159718.75</v>
+      </c>
+      <c r="E6">
+        <v>20.23959139630185</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -441,245 +486,489 @@
       <c r="B7">
         <v>947986.62</v>
       </c>
+      <c r="C7">
+        <v>847559.25</v>
+      </c>
+      <c r="D7">
+        <v>100427.37</v>
+      </c>
+      <c r="E7">
+        <v>11.84900878611142</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Osorno</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B8">
-        <v>941105.75</v>
+        <v>944701.12</v>
+      </c>
+      <c r="C8">
+        <v>842640.25</v>
+      </c>
+      <c r="D8">
+        <v>102060.87</v>
+      </c>
+      <c r="E8">
+        <v>12.11203357541963</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Chaitén</t>
+          <t>Osorno</t>
         </is>
       </c>
       <c r="B9">
-        <v>935867.9399999999</v>
+        <v>941105.75</v>
+      </c>
+      <c r="C9">
+        <v>845408.8100000001</v>
+      </c>
+      <c r="D9">
+        <v>95696.93999999994</v>
+      </c>
+      <c r="E9">
+        <v>11.31960524518309</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Curaco de Vélez</t>
+          <t>Chaitén</t>
         </is>
       </c>
       <c r="B10">
-        <v>930150</v>
+        <v>935867.9399999999</v>
+      </c>
+      <c r="C10">
+        <v>826490.5</v>
+      </c>
+      <c r="D10">
+        <v>109377.4399999999</v>
+      </c>
+      <c r="E10">
+        <v>13.23396215685479</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cochamó</t>
+          <t>Curaco de Vélez</t>
         </is>
       </c>
       <c r="B11">
-        <v>909668.0600000001</v>
+        <v>930150</v>
+      </c>
+      <c r="C11">
+        <v>824562</v>
+      </c>
+      <c r="D11">
+        <v>105588</v>
+      </c>
+      <c r="E11">
+        <v>12.80534392804908</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Futaleufú</t>
+          <t>Cochamó</t>
         </is>
       </c>
       <c r="B12">
-        <v>893820.5</v>
+        <v>909668.0600000001</v>
+      </c>
+      <c r="C12">
+        <v>813470.25</v>
+      </c>
+      <c r="D12">
+        <v>96197.81000000006</v>
+      </c>
+      <c r="E12">
+        <v>11.82560886522894</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Quellón</t>
+          <t>Futaleufú</t>
         </is>
       </c>
       <c r="B13">
-        <v>892700.62</v>
+        <v>893820.5</v>
+      </c>
+      <c r="C13">
+        <v>807867.38</v>
+      </c>
+      <c r="D13">
+        <v>85953.12</v>
+      </c>
+      <c r="E13">
+        <v>10.63950867777332</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ancud</t>
+          <t>Quellón</t>
         </is>
       </c>
       <c r="B14">
-        <v>888627.5</v>
+        <v>892700.62</v>
+      </c>
+      <c r="C14">
+        <v>804405.12</v>
+      </c>
+      <c r="D14">
+        <v>88295.5</v>
+      </c>
+      <c r="E14">
+        <v>10.97649651956467</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Llanquihue</t>
+          <t>Ancud</t>
         </is>
       </c>
       <c r="B15">
-        <v>886353.9399999999</v>
+        <v>888627.5</v>
+      </c>
+      <c r="C15">
+        <v>759527.1899999999</v>
+      </c>
+      <c r="D15">
+        <v>129100.3100000001</v>
+      </c>
+      <c r="E15">
+        <v>16.99745732605045</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Chonchi</t>
+          <t>Llanquihue</t>
         </is>
       </c>
       <c r="B16">
-        <v>879155.88</v>
+        <v>886353.9399999999</v>
+      </c>
+      <c r="C16">
+        <v>759374.0600000001</v>
+      </c>
+      <c r="D16">
+        <v>126979.8799999999</v>
+      </c>
+      <c r="E16">
+        <v>16.7216509871301</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Puqueldón</t>
+          <t>Chonchi</t>
         </is>
       </c>
       <c r="B17">
-        <v>866403.25</v>
+        <v>879155.88</v>
+      </c>
+      <c r="C17">
+        <v>774293.9399999999</v>
+      </c>
+      <c r="D17">
+        <v>104861.9400000001</v>
+      </c>
+      <c r="E17">
+        <v>13.5429111068595</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Frutillar</t>
+          <t>Puqueldón</t>
         </is>
       </c>
       <c r="B18">
-        <v>862841.0600000001</v>
+        <v>866403.25</v>
+      </c>
+      <c r="C18">
+        <v>755352.6899999999</v>
+      </c>
+      <c r="D18">
+        <v>111050.5600000001</v>
+      </c>
+      <c r="E18">
+        <v>14.70181565117614</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Calbuco</t>
+          <t>Frutillar</t>
         </is>
       </c>
       <c r="B19">
-        <v>858706.1899999999</v>
+        <v>862841.0600000001</v>
+      </c>
+      <c r="C19">
+        <v>754705</v>
+      </c>
+      <c r="D19">
+        <v>108136.0600000001</v>
+      </c>
+      <c r="E19">
+        <v>14.32825541105467</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Queilén</t>
+          <t>Calbuco</t>
         </is>
       </c>
       <c r="B20">
-        <v>856643.38</v>
+        <v>858706.1899999999</v>
+      </c>
+      <c r="C20">
+        <v>755409.88</v>
+      </c>
+      <c r="D20">
+        <v>103296.3099999999</v>
+      </c>
+      <c r="E20">
+        <v>13.67420690870498</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Quemchi</t>
+          <t>Queilén</t>
         </is>
       </c>
       <c r="B21">
-        <v>843365.1899999999</v>
+        <v>856643.38</v>
+      </c>
+      <c r="C21">
+        <v>756009.0600000001</v>
+      </c>
+      <c r="D21">
+        <v>100634.3199999999</v>
+      </c>
+      <c r="E21">
+        <v>13.31125846560621</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Dalcahue</t>
+          <t>Quemchi</t>
         </is>
       </c>
       <c r="B22">
-        <v>835448.8100000001</v>
+        <v>843365.1899999999</v>
+      </c>
+      <c r="C22">
+        <v>723181.62</v>
+      </c>
+      <c r="D22">
+        <v>120183.5699999999</v>
+      </c>
+      <c r="E22">
+        <v>16.618725735867</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Maullín</t>
+          <t>Dalcahue</t>
         </is>
       </c>
       <c r="B23">
-        <v>797679.0600000001</v>
+        <v>835448.8100000001</v>
+      </c>
+      <c r="C23">
+        <v>730986.9399999999</v>
+      </c>
+      <c r="D23">
+        <v>104461.8700000001</v>
+      </c>
+      <c r="E23">
+        <v>14.290524807461</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Río Negro</t>
+          <t>Maullín</t>
         </is>
       </c>
       <c r="B24">
-        <v>778819.4399999999</v>
+        <v>797679.0600000001</v>
+      </c>
+      <c r="C24">
+        <v>694798.5</v>
+      </c>
+      <c r="D24">
+        <v>102880.5600000001</v>
+      </c>
+      <c r="E24">
+        <v>14.80725131099161</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>San Pablo</t>
+          <t>Río Negro</t>
         </is>
       </c>
       <c r="B25">
-        <v>773275.4399999999</v>
+        <v>778819.4399999999</v>
+      </c>
+      <c r="C25">
+        <v>670506.0600000001</v>
+      </c>
+      <c r="D25">
+        <v>108313.3799999999</v>
+      </c>
+      <c r="E25">
+        <v>16.15397480523888</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Los Muermos</t>
+          <t>San Pablo</t>
         </is>
       </c>
       <c r="B26">
-        <v>767498.38</v>
+        <v>773275.4399999999</v>
+      </c>
+      <c r="C26">
+        <v>666262.0600000001</v>
+      </c>
+      <c r="D26">
+        <v>107013.3799999999</v>
+      </c>
+      <c r="E26">
+        <v>16.06175503975116</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Puerto Octay</t>
+          <t>Los Muermos</t>
         </is>
       </c>
       <c r="B27">
-        <v>763313.9399999999</v>
+        <v>767498.38</v>
+      </c>
+      <c r="C27">
+        <v>669924.5</v>
+      </c>
+      <c r="D27">
+        <v>97573.88</v>
+      </c>
+      <c r="E27">
+        <v>14.56490694100603</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Puyehue</t>
+          <t>Puerto Octay</t>
         </is>
       </c>
       <c r="B28">
-        <v>763173.9399999999</v>
+        <v>763313.9399999999</v>
+      </c>
+      <c r="C28">
+        <v>678092.3100000001</v>
+      </c>
+      <c r="D28">
+        <v>85221.62999999989</v>
+      </c>
+      <c r="E28">
+        <v>12.56785082845136</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Purranque</t>
+          <t>Puyehue</t>
         </is>
       </c>
       <c r="B29">
-        <v>759157.12</v>
+        <v>763173.9399999999</v>
+      </c>
+      <c r="C29">
+        <v>637626.38</v>
+      </c>
+      <c r="D29">
+        <v>125547.5599999999</v>
+      </c>
+      <c r="E29">
+        <v>19.68983152798664</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Fresia</t>
+          <t>Purranque</t>
         </is>
       </c>
       <c r="B30">
-        <v>743177.5600000001</v>
+        <v>759157.12</v>
+      </c>
+      <c r="C30">
+        <v>675376</v>
+      </c>
+      <c r="D30">
+        <v>83781.12</v>
+      </c>
+      <c r="E30">
+        <v>12.40510767335527</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>743177.5600000001</v>
+      </c>
+      <c r="C31">
+        <v>650079.38</v>
+      </c>
+      <c r="D31">
+        <v>93098.18000000005</v>
+      </c>
+      <c r="E31">
+        <v>14.3210479926313</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>San Juan de la Costa</t>
         </is>
       </c>
-      <c r="B31">
+      <c r="B32">
         <v>687087.88</v>
+      </c>
+      <c r="C32">
+        <v>612033.9399999999</v>
+      </c>
+      <c r="D32">
+        <v>75053.94000000006</v>
+      </c>
+      <c r="E32">
+        <v>12.26303560877686</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_a_2022_los_lagos.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_a_2022_los_lagos.xlsx
@@ -978,7 +978,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -987,310 +987,215 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ancud</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>888627.5</v>
+          <t>San Pablo</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Calbuco</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>858706.1899999999</v>
+          <t>Puqueldón</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Castro</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>975423.9399999999</v>
+          <t>Fresia</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Chaitén</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>935867.9399999999</v>
+          <t>Llanquihue</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Chonchi</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>879155.88</v>
+          <t>Osorno</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cochamó</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>909668.0600000001</v>
+          <t>Purranque</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Curaco de Vélez</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>930150</v>
+          <t>Puyehue</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dalcahue</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>835448.8100000001</v>
+          <t>Cochamó</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fresia</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>743177.5600000001</v>
+          <t>Ancud</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Frutillar</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>862841.0600000001</v>
+          <t>Quellón</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Futaleufú</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>893820.5</v>
+          <t>Queilén</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Hualaihué</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>948858.9399999999</v>
+          <t>Chonchi</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Llanquihue</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>886353.9399999999</v>
+          <t>Puerto Montt</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Los Muermos</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>767498.38</v>
+          <t>Río Negro</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Maullín</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>797679.0600000001</v>
+          <t>Castro</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Osorno</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>941105.75</v>
+          <t>Dalcahue</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Palena</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>977059.62</v>
+          <t>Quemchi</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>984058.4399999999</v>
+          <t>San Juan de la Costa</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Puerto Octay</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>763313.9399999999</v>
+          <t>Calbuco</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Puerto Varas</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>1257646.88</v>
+          <t>Chaitén</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Puqueldón</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>866403.25</v>
+          <t>Los Muermos</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Purranque</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>759157.12</v>
+          <t>Maullín</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Puyehue</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>763173.9399999999</v>
+          <t>Quinchao</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Queilén</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>856643.38</v>
+          <t>Curaco de Vélez</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Quellón</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>892700.62</v>
+          <t>Puerto Octay</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Quemchi</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>843365.1899999999</v>
+          <t>Frutillar</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Quinchao</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>947986.62</v>
+          <t>Puerto Varas</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Río Negro</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>778819.4399999999</v>
+          <t>Hualaihué</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>San Juan de la Costa</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>687087.88</v>
+          <t>Palena</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>San Pablo</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>773275.4399999999</v>
+          <t>Futaleufú</t>
+        </is>
       </c>
     </row>
   </sheetData>
